--- a/ci-build/cm-sct-to-obds-grading.xlsx
+++ b/ci-build/cm-sct-to-obds-grading.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-03T20:30:38+00:00</t>
+    <t>2026-05-03T21:28:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/cm-sct-to-obds-grading.xlsx
+++ b/ci-build/cm-sct-to-obds-grading.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-03T21:28:00+00:00</t>
+    <t>2026-05-04T06:23:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/cm-sct-to-obds-grading.xlsx
+++ b/ci-build/cm-sct-to-obds-grading.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T06:23:23+00:00</t>
+    <t>2026-05-04T06:44:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/cm-sct-to-obds-grading.xlsx
+++ b/ci-build/cm-sct-to-obds-grading.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T06:44:52+00:00</t>
+    <t>2026-05-04T07:06:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/cm-sct-to-obds-grading.xlsx
+++ b/ci-build/cm-sct-to-obds-grading.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:06:34+00:00</t>
+    <t>2026-05-04T07:30:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/cm-sct-to-obds-grading.xlsx
+++ b/ci-build/cm-sct-to-obds-grading.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:30:32+00:00</t>
+    <t>2026-05-04T07:50:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/cm-sct-to-obds-grading.xlsx
+++ b/ci-build/cm-sct-to-obds-grading.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:50:36+00:00</t>
+    <t>2026-05-04T08:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/cm-sct-to-obds-grading.xlsx
+++ b/ci-build/cm-sct-to-obds-grading.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T08:11:13+00:00</t>
+    <t>2026-05-04T08:32:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/cm-sct-to-obds-grading.xlsx
+++ b/ci-build/cm-sct-to-obds-grading.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T08:32:13+00:00</t>
+    <t>2026-05-04T09:30:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/cm-sct-to-obds-grading.xlsx
+++ b/ci-build/cm-sct-to-obds-grading.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T09:30:07+00:00</t>
+    <t>2026-05-04T09:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/cm-sct-to-obds-grading.xlsx
+++ b/ci-build/cm-sct-to-obds-grading.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T09:51:52+00:00</t>
+    <t>2026-05-04T11:25:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/cm-sct-to-obds-grading.xlsx
+++ b/ci-build/cm-sct-to-obds-grading.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T11:25:12+00:00</t>
+    <t>2026-05-04T11:47:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/cm-sct-to-obds-grading.xlsx
+++ b/ci-build/cm-sct-to-obds-grading.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T11:47:21+00:00</t>
+    <t>2026-05-04T12:11:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/cm-sct-to-obds-grading.xlsx
+++ b/ci-build/cm-sct-to-obds-grading.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T12:11:06+00:00</t>
+    <t>2026-05-04T13:22:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/cm-sct-to-obds-grading.xlsx
+++ b/ci-build/cm-sct-to-obds-grading.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T13:22:07+00:00</t>
+    <t>2026-05-04T13:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/cm-sct-to-obds-grading.xlsx
+++ b/ci-build/cm-sct-to-obds-grading.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T13:47:49+00:00</t>
+    <t>2026-05-04T14:15:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/cm-sct-to-obds-grading.xlsx
+++ b/ci-build/cm-sct-to-obds-grading.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:15:24+00:00</t>
+    <t>2026-05-04T14:55:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/cm-sct-to-obds-grading.xlsx
+++ b/ci-build/cm-sct-to-obds-grading.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:55:41+00:00</t>
+    <t>2026-05-04T15:18:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/cm-sct-to-obds-grading.xlsx
+++ b/ci-build/cm-sct-to-obds-grading.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T15:18:17+00:00</t>
+    <t>2026-05-04T15:40:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/cm-sct-to-obds-grading.xlsx
+++ b/ci-build/cm-sct-to-obds-grading.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T18:43:40+00:00</t>
+    <t>2026-05-12T08:39:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/cm-sct-to-obds-grading.xlsx
+++ b/ci-build/cm-sct-to-obds-grading.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T08:39:42+00:00</t>
+    <t>2026-05-12T14:42:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
